--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9</t>
+    <t>9999</t>
   </si>
 </sst>
 </file>
@@ -132,14 +132,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,148 +588,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9999</t>
+    <t>9</t>
   </si>
 </sst>
 </file>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9</t>
+    <t>9999</t>
   </si>
 </sst>
 </file>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9</t>
+    <t>9999</t>
   </si>
 </sst>
 </file>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9999</t>
+    <t>9,9999</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1252,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9,9999</t>
+    <t>9999</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1252,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -1252,7 +1252,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1088,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -41,15 +41,6 @@
     <t>EnemyName</t>
   </si>
   <si>
-    <t>MinPopulation</t>
-  </si>
-  <si>
-    <t>MaxPopulation</t>
-  </si>
-  <si>
-    <t>WaveCount</t>
-  </si>
-  <si>
     <t>ChessIds</t>
   </si>
   <si>
@@ -59,15 +50,12 @@
     <t>Spacing</t>
   </si>
   <si>
-    <t>DifficultyMultiplier</t>
-  </si>
-  <si>
-    <t>RewardMultiplier</t>
-  </si>
-  <si>
     <t>TimeLimit</t>
   </si>
   <si>
+    <t>ChessIds_Boss</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -89,15 +77,6 @@
     <t>敌人名称</t>
   </si>
   <si>
-    <t>（对战时）最小人口数</t>
-  </si>
-  <si>
-    <t>（对战时）最大人口数</t>
-  </si>
-  <si>
-    <t>波次数量</t>
-  </si>
-  <si>
     <t>棋子ID列表</t>
   </si>
   <si>
@@ -107,19 +86,25 @@
     <t>棋子间距（米）</t>
   </si>
   <si>
-    <t>难度倍率（影响棋子属性）</t>
-  </si>
-  <si>
-    <t>奖励倍率</t>
-  </si>
-  <si>
     <t>战斗时间限制（秒，0=无限制）</t>
   </si>
   <si>
+    <t>Boss模式棋子波次列表（格式：波1_敌人1,敌人2|波2_敌人3,敌人4）</t>
+  </si>
+  <si>
     <t>后羿测试</t>
   </si>
   <si>
-    <t>10</t>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>Boss敌人-王者</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1,3,1|2,3,2|3,4</t>
   </si>
 </sst>
 </file>
@@ -132,7 +117,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,148 +580,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1087,24 +1079,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,17 +1102,13 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="E1" s="2"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,7 +1119,7 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1143,140 +1128,115 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" ht="27" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:13">
+    <row r="5" ht="15" customHeight="1" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="1">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:9">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="G6" s="1">
         <v>2.5</v>
       </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="H6" s="1">
         <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -95,7 +95,7 @@
     <t>后羿测试</t>
   </si>
   <si>
-    <t>9999</t>
+    <t>10</t>
   </si>
   <si>
     <t>Boss敌人-王者</t>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -92,13 +92,25 @@
     <t>Boss模式棋子波次列表（格式：波1_敌人1,敌人2|波2_敌人3,敌人4）</t>
   </si>
   <si>
-    <t>后羿测试</t>
+    <t>邪灵-普通</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>Boss敌人-王者</t>
+    <t>恶魂-普通</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>邪灵-精英</t>
+  </si>
+  <si>
+    <t>恶魂-精英</t>
+  </si>
+  <si>
+    <t>黑暗杨戬-Boss</t>
   </si>
   <si>
     <t>0</t>
@@ -1079,8 +1091,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1235,8 +1247,77 @@
       <c r="H6" s="1">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:9">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:9">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:9">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/EnemyTable.xlsx
+++ b/AAAGameData/DataTables/EnemyTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -116,7 +116,25 @@
     <t>0</t>
   </si>
   <si>
-    <t>1,3,1|2,3,2|3,4</t>
+    <t>10,12,10</t>
+  </si>
+  <si>
+    <t>黑化后羿-普通</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>黑化后羿-精英</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-普通</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>黑化嫦娥-精英</t>
   </si>
 </sst>
 </file>
@@ -1091,8 +1109,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1174,7 +1192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:9">
+    <row r="4" ht="28.8" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1320,6 +1338,98 @@
         <v>29</v>
       </c>
     </row>
+    <row r="10" ht="15" customHeight="1" spans="1:9">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:9">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:9">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:9">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
